--- a/cert-data/Healthcare-Certification-Report-10.20.2026.xlsx
+++ b/cert-data/Healthcare-Certification-Report-10.20.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://konicaminoltanam-my.sharepoint.com/personal/rnesimi_kmbsus_com/Documents/Dashboard Reports/Healthcare Dashboard Reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FD48F8C-807C-4861-ADE0-B1EF40F17BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{18D0BB39-5CB6-4529-8517-DB19948572A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC5E560D-579C-485D-825F-94F306B9108B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC5E560D-579C-485D-825F-94F306B9108B}"/>
   </bookViews>
   <sheets>
     <sheet name="Healthcare Certification Report" sheetId="1" r:id="rId1"/>
@@ -2443,9 +2443,18 @@
       <c r="Q3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="R3" s="1"/>
-      <c r="T3" s="11" t="s">
-        <v>36</v>
+      <c r="R3" s="9">
+        <v>46315</v>
+      </c>
+      <c r="S3" s="1" t="str">
+        <f>"FY"&amp;YEAR(R3)-IF(MONTH(R3)&lt;4,1,0)&amp;" "&amp;CHOOSE(MATCH(MONTH(R3),{1,4,7,10}),"Q4","Q1","Q2","Q3")</f>
+        <v>FY2026 Q3</v>
+      </c>
+      <c r="T3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="U3" s="4">
+        <v>3.95</v>
       </c>
     </row>
     <row r="4" spans="1:21">
